--- a/reports/pdf_weekly_20260717.xlsx
+++ b/reports/pdf_weekly_20260717.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      주말 2026-07-17  vs  주초 2026-07-13      매수 13종목  /  매도 17종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,921억   ·   현금 124억(2.5%)      주말 2026-07-17  vs  주초 2026-07-13      매수 13종목  /  매도 17종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -664,10 +664,8 @@
       <c r="B6" s="11" t="n">
         <v>263</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="11" t="n">
+        <v>4093458240</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -687,10 +685,8 @@
       <c r="H6" s="15" t="n">
         <v>-78</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="15" t="n">
+        <v>-3245923200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -712,10 +708,8 @@
       <c r="B7" s="11" t="n">
         <v>223</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="11" t="n">
+        <v>9733504000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,10 +729,8 @@
       <c r="H7" s="15" t="n">
         <v>-69</v>
       </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="15" t="n">
+        <v>-923363520</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -760,10 +752,8 @@
       <c r="B8" s="11" t="n">
         <v>152</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="11" t="n">
+        <v>1528949760</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -783,10 +773,8 @@
       <c r="H8" s="15" t="n">
         <v>-61</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="15" t="n">
+        <v>-1857718400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -808,10 +796,8 @@
       <c r="B9" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="11" t="n">
+        <v>5072691200</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -831,10 +817,8 @@
       <c r="H9" s="15" t="n">
         <v>-54</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="15" t="n">
+        <v>-918691200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -856,10 +840,8 @@
       <c r="B10" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="11" t="n">
+        <v>1118470080</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -879,10 +861,8 @@
       <c r="H10" s="15" t="n">
         <v>-39</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="15" t="n">
+        <v>-1849286400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -904,10 +884,8 @@
       <c r="B11" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="11" t="n">
+        <v>484492800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -927,10 +905,8 @@
       <c r="H11" s="15" t="n">
         <v>-30</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="15" t="n">
+        <v>-785664000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -952,10 +928,8 @@
       <c r="B12" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="11" t="n">
+        <v>722126400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -975,10 +949,8 @@
       <c r="H12" s="15" t="n">
         <v>-20</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="15" t="n">
+        <v>-1343168000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -1000,10 +972,8 @@
       <c r="B13" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="11" t="n">
+        <v>2944057600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -1023,10 +993,8 @@
       <c r="H13" s="15" t="n">
         <v>-17</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="15" t="n">
+        <v>-3608896000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1048,10 +1016,8 @@
       <c r="B14" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="11" t="n">
+        <v>980294400</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1071,10 +1037,8 @@
       <c r="H14" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="15" t="n">
+        <v>-463512000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1096,10 +1060,8 @@
       <c r="B15" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="11" t="n">
+        <v>952816000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1119,10 +1081,8 @@
       <c r="H15" s="15" t="n">
         <v>-15</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="15" t="n">
+        <v>-433008000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1144,10 +1104,8 @@
       <c r="B16" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="11" t="n">
+        <v>475564800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1167,10 +1125,8 @@
       <c r="H16" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="15" t="n">
+        <v>-428147200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1192,10 +1148,8 @@
       <c r="B17" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="11" t="n">
+        <v>461032000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1215,10 +1169,8 @@
       <c r="H17" s="15" t="n">
         <v>-11</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="15" t="n">
+        <v>-896966400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1240,10 +1192,8 @@
       <c r="B18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C18" s="11" t="n">
+        <v>497289600</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1263,10 +1213,8 @@
       <c r="H18" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="15" t="n">
+        <v>-430528000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1293,10 +1241,8 @@
       <c r="H19" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="15" t="n">
+        <v>-1483833600</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1323,10 +1269,8 @@
       <c r="H20" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="15" t="n">
+        <v>-990908800</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1353,10 +1297,8 @@
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="15" t="n">
+        <v>-230640000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1383,10 +1325,8 @@
       <c r="H22" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="15" t="n">
+        <v>-390451200</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1402,7 +1342,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      주말 2026-07-17  vs  주초 2026-07-13      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,238억   ·   현금 23억(0.5%)      주말 2026-07-17  vs  주초 2026-07-13      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1497,10 +1437,8 @@
       <c r="B27" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="11" t="n">
+        <v>586673880</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1520,10 +1458,8 @@
       <c r="H27" s="15" t="n">
         <v>-49</v>
       </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="15" t="n">
+        <v>-884697450</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1545,10 +1481,8 @@
       <c r="B28" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="11" t="n">
+        <v>1265390100</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1568,10 +1502,8 @@
       <c r="H28" s="15" t="n">
         <v>-21</v>
       </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="15" t="n">
+        <v>-401495850</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1593,10 +1525,8 @@
       <c r="B29" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="11" t="n">
+        <v>1023021000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1616,10 +1546,8 @@
       <c r="H29" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="15" t="n">
+        <v>-861678000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1669,7 +1597,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      주말 2026-07-17  vs  주초 2026-07-13      매수 6종목  /  매도 11종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 359억   ·   현금 4억(100.0%)      주말 2026-07-17  vs  주초 2026-07-13      매수 6종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1764,14 +1692,12 @@
       <c r="B38" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="11" t="n">
+        <v>76015500</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.67%→6.88%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1787,14 +1713,12 @@
       <c r="H38" s="15" t="n">
         <v>-174</v>
       </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="15" t="n">
+        <v>-42225450</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.44%→0.31%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1812,14 +1736,12 @@
       <c r="B39" s="11" t="n">
         <v>96</v>
       </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="11" t="n">
+        <v>320688000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.33%→7.28%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1835,14 +1757,12 @@
       <c r="H39" s="15" t="n">
         <v>-29</v>
       </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="15" t="n">
+        <v>-19448850</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.37%→0.31%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1860,14 +1780,12 @@
       <c r="B40" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="11" t="n">
+        <v>191568750</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.32%→5.88%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1877,25 +1795,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="15" t="n">
+        <v>-50468750</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -1908,14 +1824,12 @@
       <c r="B41" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="11" t="n">
+        <v>122536000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.48%→2.84%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1925,25 +1839,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-25</v>
       </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="15" t="n">
+        <v>-37888750</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
@@ -1956,14 +1868,12 @@
       <c r="B42" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="11" t="n">
+        <v>125647000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.37%→2.74%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1979,14 +1889,12 @@
       <c r="H42" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="15" t="n">
+        <v>-33753500</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -2004,14 +1912,12 @@
       <c r="B43" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="11" t="n">
+        <v>36040000</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11%→0.22%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2027,14 +1933,12 @@
       <c r="H43" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="15" t="n">
+        <v>-158457000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.64%→3.16%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -2057,14 +1961,12 @@
       <c r="H44" s="15" t="n">
         <v>-12</v>
       </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" s="15" t="n">
+        <v>-143514000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.47%→3.03%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2087,14 +1989,12 @@
       <c r="H45" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="15" t="n">
+        <v>-148639500</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.75%→3.30%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2117,14 +2017,12 @@
       <c r="H46" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="15" t="n">
+        <v>-82849500</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.13%→3.87%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -2147,14 +2045,12 @@
       <c r="H47" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="15" t="n">
+        <v>-86275000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.77%→1.51%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -2177,14 +2073,12 @@
       <c r="H48" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="15" t="n">
+        <v>-54825000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.57%→2.40%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2196,7 +2090,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      주말 2026-07-17  vs  주초 2026-07-13      매수 1종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 18억(3.2%)      주말 2026-07-17  vs  주초 2026-07-13      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -2291,10 +2185,8 @@
       <c r="B53" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="11" t="n">
+        <v>529461120</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_weekly_20260717.xlsx
+++ b/reports/pdf_weekly_20260717.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>알멕  (편출)</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-463512000</v>
+        <v>-433008000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.58%→0.45%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>15→0</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>알멕  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-433008000</v>
+        <v>-463512000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.45%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>15→0</t>
         </is>
       </c>
     </row>
@@ -1795,23 +1795,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-50468750</v>
+        <v>-37888750</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.42%</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-37888750</v>
+        <v>-50468750</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.28%</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -1983,23 +1983,23 @@
       <c r="E45" s="17" t="n"/>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-148639500</v>
+        <v>-82849500</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>3.75%→3.30%</t>
+          <t>4.13%→3.87%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>
@@ -2011,23 +2011,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-82849500</v>
+        <v>-148639500</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>4.13%→3.87%</t>
+          <t>3.75%→3.30%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260717.xlsx
+++ b/reports/pdf_weekly_20260717.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>알멕  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-433008000</v>
+        <v>-463512000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.45%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>15→0</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알멕  (편출)</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-463512000</v>
+        <v>-433008000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.58%→0.45%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>15→0</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
@@ -1795,23 +1795,23 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-37888750</v>
+        <v>-50468750</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.28%</t>
+          <t>0.57%→0.42%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -1839,23 +1839,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-50468750</v>
+        <v>-37888750</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.57%→0.42%</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260717.xlsx
+++ b/reports/pdf_weekly_20260717.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>알멕  (편출)</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-463512000</v>
+        <v>-433008000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.58%→0.45%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>15→0</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>알멕  (편출)</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-433008000</v>
+        <v>-463512000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.45%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>15→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_weekly_20260717.xlsx
+++ b/reports/pdf_weekly_20260717.xlsx
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀</t>
+          <t>알멕  (편출)</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-433008000</v>
+        <v>-463512000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.45%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>90→75</t>
+          <t>15→0</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>알멕  (편출)</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-463512000</v>
+        <v>-433008000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.58%→0.45%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>15→0</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
@@ -1983,23 +1983,23 @@
       <c r="E45" s="17" t="n"/>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-82849500</v>
+        <v>-148639500</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>4.13%→3.87%</t>
+          <t>3.75%→3.30%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>150→141</t>
+          <t>76→67</t>
         </is>
       </c>
     </row>
@@ -2011,23 +2011,23 @@
       <c r="E46" s="17" t="n"/>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-148639500</v>
+        <v>-82849500</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>3.75%→3.30%</t>
+          <t>4.13%→3.87%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>76→67</t>
+          <t>150→141</t>
         </is>
       </c>
     </row>
